--- a/artfynd/A 31325-2023 artfynd.xlsx
+++ b/artfynd/A 31325-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31325-2023 artfynd.xlsx
+++ b/artfynd/A 31325-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113038081</v>
+        <v>113037760</v>
       </c>
       <c r="B3" t="n">
-        <v>96271</v>
+        <v>90003</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +807,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>5445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580371</v>
+        <v>580241</v>
       </c>
       <c r="R3" t="n">
-        <v>6339422</v>
+        <v>6339253</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -908,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113037760</v>
+        <v>113037796</v>
       </c>
       <c r="B4" t="n">
-        <v>90003</v>
+        <v>78713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,28 +931,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5445</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -955,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580241</v>
+        <v>580298</v>
       </c>
       <c r="R4" t="n">
-        <v>6339253</v>
+        <v>6339464</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113037796</v>
+        <v>113037954</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
+        <v>56781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,26 +1047,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580298</v>
+        <v>580349</v>
       </c>
       <c r="R5" t="n">
-        <v>6339464</v>
+        <v>6339636</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,7 +1137,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1144,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113037954</v>
+        <v>113037987</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>55826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,20 +1167,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,7 +1197,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1268,10 +1279,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113037987</v>
+        <v>113037976</v>
       </c>
       <c r="B7" t="n">
-        <v>55826</v>
+        <v>56681</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,20 +1291,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100045</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,7 +1321,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1392,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113037976</v>
+        <v>113037942</v>
       </c>
       <c r="B8" t="n">
-        <v>56681</v>
+        <v>78713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,35 +1419,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1498,6 +1500,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1516,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113037942</v>
+        <v>113037968</v>
       </c>
       <c r="B9" t="n">
-        <v>78713</v>
+        <v>56784</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,30 +1531,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>102977</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1613,7 +1625,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1632,10 +1643,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113037968</v>
+        <v>113084856</v>
       </c>
       <c r="B10" t="n">
-        <v>56784</v>
+        <v>94120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,46 +1659,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävhällsberget, Boda, Sm</t>
+          <t>Bosjön, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580349</v>
+        <v>580542</v>
       </c>
       <c r="R10" t="n">
-        <v>6339636</v>
+        <v>6339431</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1714,22 +1714,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1744,22 +1734,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Brenander, Anneli Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113084856</v>
+        <v>113080291</v>
       </c>
       <c r="B11" t="n">
-        <v>94120</v>
+        <v>90273</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,25 +1758,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1797,10 +1787,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580542</v>
+        <v>580428</v>
       </c>
       <c r="R11" t="n">
-        <v>6339431</v>
+        <v>6339496</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1859,7 +1849,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113080291</v>
+        <v>113079428</v>
       </c>
       <c r="B12" t="n">
         <v>90273</v>
@@ -1900,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580428</v>
+        <v>580416</v>
       </c>
       <c r="R12" t="n">
-        <v>6339496</v>
+        <v>6339498</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1962,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113079428</v>
+        <v>113080793</v>
       </c>
       <c r="B13" t="n">
-        <v>90273</v>
+        <v>56782</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,21 +1968,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1101</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2003,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580416</v>
+        <v>580446</v>
       </c>
       <c r="R13" t="n">
-        <v>6339498</v>
+        <v>6339507</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2039,6 +2029,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-11-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113080793</v>
+        <v>113085321</v>
       </c>
       <c r="B14" t="n">
-        <v>56782</v>
+        <v>78332</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,39 +2072,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1639</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bosjön, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580446</v>
+        <v>580607</v>
       </c>
       <c r="R14" t="n">
-        <v>6339507</v>
+        <v>6339418</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2144,17 +2141,13 @@
           <t>2023-11-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2173,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113085321</v>
+        <v>113083421</v>
       </c>
       <c r="B15" t="n">
-        <v>78332</v>
+        <v>90670</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,37 +2182,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1639</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bosjön, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580607</v>
+        <v>580489</v>
       </c>
       <c r="R15" t="n">
-        <v>6339418</v>
+        <v>6339483</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2260,7 +2251,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2279,10 +2269,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113083421</v>
+        <v>113085016</v>
       </c>
       <c r="B16" t="n">
-        <v>90670</v>
+        <v>91341</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,25 +2281,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1339</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2310,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580489</v>
+        <v>580571</v>
       </c>
       <c r="R16" t="n">
-        <v>6339483</v>
+        <v>6339394</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2382,10 +2372,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113085016</v>
+        <v>113079950</v>
       </c>
       <c r="B17" t="n">
-        <v>91341</v>
+        <v>56782</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,21 +2388,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2423,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580571</v>
+        <v>580428</v>
       </c>
       <c r="R17" t="n">
-        <v>6339394</v>
+        <v>6339496</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2485,10 +2475,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113079950</v>
+        <v>113081275</v>
       </c>
       <c r="B18" t="n">
-        <v>56782</v>
+        <v>90077</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,21 +2491,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580428</v>
+        <v>580366</v>
       </c>
       <c r="R18" t="n">
-        <v>6339496</v>
+        <v>6339627</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2588,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113081275</v>
+        <v>113084949</v>
       </c>
       <c r="B19" t="n">
-        <v>90077</v>
+        <v>91341</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580366</v>
+        <v>580559</v>
       </c>
       <c r="R19" t="n">
-        <v>6339627</v>
+        <v>6339396</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113084949</v>
+        <v>113081096</v>
       </c>
       <c r="B20" t="n">
-        <v>91341</v>
+        <v>90077</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2697,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,10 +2722,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580559</v>
+        <v>580408</v>
       </c>
       <c r="R20" t="n">
-        <v>6339396</v>
+        <v>6339608</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2794,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113081096</v>
+        <v>113080310</v>
       </c>
       <c r="B21" t="n">
-        <v>90077</v>
+        <v>90057</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2810,21 +2800,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2835,10 +2825,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580408</v>
+        <v>580428</v>
       </c>
       <c r="R21" t="n">
-        <v>6339608</v>
+        <v>6339496</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2897,10 +2887,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113080310</v>
+        <v>113085863</v>
       </c>
       <c r="B22" t="n">
-        <v>90057</v>
+        <v>78332</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2909,25 +2899,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1639</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,10 +2928,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580428</v>
+        <v>580463</v>
       </c>
       <c r="R22" t="n">
-        <v>6339496</v>
+        <v>6339313</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,10 +2990,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113085863</v>
+        <v>113080115</v>
       </c>
       <c r="B23" t="n">
-        <v>78332</v>
+        <v>90273</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3012,25 +3002,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1639</v>
+        <v>1101</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3041,10 +3031,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580463</v>
+        <v>580438</v>
       </c>
       <c r="R23" t="n">
-        <v>6339313</v>
+        <v>6339493</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3103,10 +3093,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113080115</v>
+        <v>113078285</v>
       </c>
       <c r="B24" t="n">
-        <v>90273</v>
+        <v>56785</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3115,25 +3105,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>102977</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580438</v>
+        <v>580319</v>
       </c>
       <c r="R24" t="n">
-        <v>6339493</v>
+        <v>6339433</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3206,10 +3196,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113078285</v>
+        <v>113084825</v>
       </c>
       <c r="B25" t="n">
-        <v>56785</v>
+        <v>94882</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3218,25 +3208,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102977</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3247,10 +3237,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580319</v>
+        <v>580542</v>
       </c>
       <c r="R25" t="n">
-        <v>6339433</v>
+        <v>6339431</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3309,10 +3299,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113084825</v>
+        <v>113084738</v>
       </c>
       <c r="B26" t="n">
-        <v>94882</v>
+        <v>56782</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3325,35 +3315,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bosjön, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580542</v>
+        <v>580507</v>
       </c>
       <c r="R26" t="n">
-        <v>6339431</v>
+        <v>6339412</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3412,10 +3410,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113084738</v>
+        <v>113082098</v>
       </c>
       <c r="B27" t="n">
-        <v>56782</v>
+        <v>90673</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3424,47 +3422,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bosjön, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580507</v>
+        <v>580512</v>
       </c>
       <c r="R27" t="n">
-        <v>6339412</v>
+        <v>6339530</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3523,10 +3513,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113082098</v>
+        <v>113081982</v>
       </c>
       <c r="B28" t="n">
-        <v>90673</v>
+        <v>56785</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3539,21 +3529,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3564,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580512</v>
+        <v>580493</v>
       </c>
       <c r="R28" t="n">
-        <v>6339530</v>
+        <v>6339542</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3623,109 +3613,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>113081982</v>
-      </c>
-      <c r="B29" t="n">
-        <v>56785</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>102977</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Gröngöling</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picus viridis</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Bosjön, Sm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>580493</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6339542</v>
-      </c>
-      <c r="S29" t="n">
-        <v>25</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2023-11-04</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2023-11-04</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
